--- a/docs/language-review/fr-fr/template/fr-fr-interface-review-v3.3.0.xlsx
+++ b/docs/language-review/fr-fr/template/fr-fr-interface-review-v3.3.0.xlsx
@@ -1140,7 +1140,7 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>Corrigé : six questions affichaient deux fois la même réponse — deux options anglaises différentes s’étaient réduites à un seul mot en espagnol ou en portugais (« tomorrow » et « morning » devenant tous les deux *mañana*, « song » et « music » tous les deux *música*), si bien que choisir la deuxième copie était compté faux. Dans l’une d’elles, *yesterday* était en plus traduit par *avion*.</t>
+          <t>Corrigé : six questions affichaient deux fois la même réponse — deux options anglaises différentes s’étaient réduites à un seul mot en espagnol ou en portugais (« tomorrow » et « morning » devenant tous les deux *mañana*, « song » et « music » tous les deux *música*), si bien que choisir la deuxième copie était compté faux. Dans l’une d’elles, *yesterday* était en plus traduit par *avion*.</t>
         </is>
       </c>
       <c r="F6" s="22" t="n"/>
